--- a/AAII_Financials/Quarterly/SCWX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCWX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,405 +656,417 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45233</v>
+      </c>
+      <c r="E7" s="2">
         <v>45142</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45051</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44960</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44862</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44771</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44680</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44589</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44498</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44407</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44225</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44134</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43952</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43770</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43679</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43588</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43497</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43406</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43315</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43224</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43133</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43042</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42951</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42860</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42769</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>89400</v>
+      </c>
+      <c r="E8" s="3">
         <v>93000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>94400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>115300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>110900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>116200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>121000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>127900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>133700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>134200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>139500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>139700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>141600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>138500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>141200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>142000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>141300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>136600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>132800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>130700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>133100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>128800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>126200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>120900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>117100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>116200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>113700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>118900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>107100</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E9" s="3">
         <v>40100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>42800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>46500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>45600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>49600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>49400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>50500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>52900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>56500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>57200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>59700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>59600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>59900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>62900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>64800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>61600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>63600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>62800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>60900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>62100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>62500</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>60500</v>
       </c>
       <c r="Z9" s="3">
         <v>60500</v>
       </c>
       <c r="AA9" s="3">
+        <v>60500</v>
+      </c>
+      <c r="AB9" s="3">
         <v>55300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>55900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>53600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>56200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E10" s="3">
         <v>52900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>51600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>68800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>65300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>66600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>71600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>77400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>80800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>77700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>82300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>80000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>82000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>78600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>78300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>77200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>79700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>73000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>70000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>69800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>71000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>66300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>65700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>60400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>61800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>60300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>60100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>62700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>53500</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1086,97 +1098,101 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E12" s="3">
         <v>28200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>31200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>37600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>35300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>33600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>33300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>31200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>32800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>30400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>28200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>29200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>27600</v>
-      </c>
-      <c r="P12" s="3">
-        <v>24100</v>
       </c>
       <c r="Q12" s="3">
         <v>24100</v>
       </c>
       <c r="R12" s="3">
+        <v>24100</v>
+      </c>
+      <c r="S12" s="3">
         <v>23400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>24100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>24900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>22600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>21700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>21100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>22500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>22400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>43000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>19500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>19700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>19500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>32400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1264,22 +1280,25 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>14200</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>15500</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>24</v>
@@ -1296,8 +1315,8 @@
       <c r="L14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1353,8 +1372,11 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1442,8 +1464,11 @@
       <c r="AE15" s="3">
         <v>3500</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1472,186 +1497,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>108600</v>
+      </c>
+      <c r="E17" s="3">
         <v>134100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>130700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>168800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>146900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>148400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>147400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>143100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>149100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>148100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>147300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>153900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>146500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>141400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>152000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>154500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>151500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>151700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>147300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>141100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>139600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>142900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>143800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>141300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>131800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>132200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>132700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>131000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-19200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-41100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-36300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-53500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-36000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-32200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-26400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-15200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-15400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-14200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-10800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-12500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-10200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-15100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-14500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-10400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-6500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-14100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-17600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-20400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-14700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-19000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-12100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-14900</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1683,186 +1715,193 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
-      </c>
-      <c r="W20" s="3">
-        <v>1000</v>
       </c>
       <c r="X20" s="3">
         <v>1000</v>
       </c>
       <c r="Y20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-32800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-29100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-42000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-27500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-23000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-17700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-5900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-6100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-4600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-5900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-9400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1950,186 +1989,195 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-18600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-41800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-38100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-50900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-36700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-32100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-27100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-16100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-8800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-14100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-12600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-11400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-13100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-14200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-13200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-17100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-22100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-14600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-16400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-19600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-11900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-13700</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-9400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-7100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-10900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-8500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-7400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-5500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-7700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-4600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-7400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-3500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-2800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-5900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-17700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-6400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2217,186 +2265,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-32400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-31000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-40000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-28100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-24700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-21600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-8800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-11800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-6400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-10300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-8300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-11800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-9400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-10300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-13300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-32400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-31000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-40000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-28100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-24700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-21600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-8800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-11800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-6400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-10300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-11800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-9400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-10300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-13300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2484,8 +2541,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2534,8 +2594,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>24</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>24</v>
@@ -2543,8 +2603,8 @@
       <c r="U29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="V29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
@@ -2553,13 +2613,13 @@
         <v>0</v>
       </c>
       <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-400</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>27000</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>24</v>
@@ -2573,8 +2633,11 @@
       <c r="AE29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2662,8 +2725,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2751,186 +2817,195 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
         <v>700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
-      </c>
-      <c r="W32" s="3">
-        <v>-1000</v>
       </c>
       <c r="X32" s="3">
         <v>-1000</v>
       </c>
       <c r="Y32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-32400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-31000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-40000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-28100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-24700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-21600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-8800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-6400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-10300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-11800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-13800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>22500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-9400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-10300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-13300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3018,191 +3093,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-32400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-31000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-40000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-28100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-24700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-21600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-8800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-6400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-10300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-11800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-13800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>22500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-9400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-10300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-13300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45233</v>
+      </c>
+      <c r="E38" s="2">
         <v>45142</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45051</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44960</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44862</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44771</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44680</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44589</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44498</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44407</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44225</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44134</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43952</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43770</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43679</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43588</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43497</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43406</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43315</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43224</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43133</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43042</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42951</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42860</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42769</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3234,8 +3318,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3267,97 +3352,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>58100</v>
+      </c>
+      <c r="E41" s="3">
         <v>64900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>94500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>143500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>139000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>167500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>186200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>220700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>205100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>197000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>180600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>220300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>188000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>181500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>156000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>181800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>138800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>117700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>111200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>129600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>115800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>103300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>77300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>101500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>99700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>97800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>91600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>116600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>110800</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3445,97 +3534,103 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>55900</v>
+      </c>
+      <c r="E43" s="3">
         <v>56400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>57000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>72600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>64100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>71300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>74900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>86200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>95100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>97800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>94900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>108000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>107900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>108400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>116800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>111800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>118400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>120100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>135300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>141300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>134400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>133300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>146800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>157800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>136600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>122700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>123200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>113500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3543,266 +3638,275 @@
         <v>800</v>
       </c>
       <c r="E44" s="3">
+        <v>800</v>
+      </c>
+      <c r="F44" s="3">
         <v>700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>400</v>
-      </c>
-      <c r="J44" s="3">
-        <v>500</v>
       </c>
       <c r="K44" s="3">
         <v>500</v>
       </c>
       <c r="L44" s="3">
+        <v>500</v>
+      </c>
+      <c r="M44" s="3">
         <v>600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>600</v>
-      </c>
-      <c r="O44" s="3">
-        <v>700</v>
       </c>
       <c r="P44" s="3">
         <v>700</v>
       </c>
       <c r="Q44" s="3">
+        <v>700</v>
+      </c>
+      <c r="R44" s="3">
         <v>800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>500</v>
-      </c>
-      <c r="W44" s="3">
-        <v>600</v>
       </c>
       <c r="X44" s="3">
         <v>600</v>
       </c>
       <c r="Y44" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z44" s="3">
         <v>700</v>
-      </c>
-      <c r="Z44" s="3">
-        <v>1000</v>
       </c>
       <c r="AA44" s="3">
         <v>1000</v>
       </c>
       <c r="AB44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC44" s="3">
         <v>1200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E45" s="3">
         <v>17400</v>
-      </c>
-      <c r="E45" s="3">
-        <v>17500</v>
       </c>
       <c r="F45" s="3">
         <v>17500</v>
       </c>
       <c r="G45" s="3">
+        <v>17500</v>
+      </c>
+      <c r="H45" s="3">
         <v>26200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>27300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>27100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>26000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>17100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>26000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>28100</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>27400</v>
       </c>
       <c r="R45" s="3">
         <v>27400</v>
       </c>
       <c r="S45" s="3">
+        <v>27400</v>
+      </c>
+      <c r="T45" s="3">
         <v>26200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>24600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>24900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>27600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>41100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>40800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>42100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>40600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>27800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>51000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>51500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>47800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>127600</v>
+      </c>
+      <c r="E46" s="3">
         <v>139500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>169700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>234300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>229900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>266600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>288600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>333400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>315300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>312600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>293100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>346200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>322600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>318700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>301000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>321800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>284300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>263500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>271900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>299000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>291900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>278100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>266900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>300900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>265100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>272600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>267700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>279800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>248500</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3890,186 +3994,195 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E48" s="3">
         <v>9000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>23400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>30000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>36500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>39500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>42100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>43600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>46700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>51100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>54600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>58200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>62800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>36000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>31100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>32600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>32500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>66900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>34000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>32800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>31200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>62300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>27600</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>512200</v>
+      </c>
+      <c r="E49" s="3">
         <v>518100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>524800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>531700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>539100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>547000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>553500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>559700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>566100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>572300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>578500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>583700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>590200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>582400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>589600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>596500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>603600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>609100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>616000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>622900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>629900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>636800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>643700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>650700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>657600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>664500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>671500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>678400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>685300</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4157,8 +4270,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4246,97 +4362,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>72200</v>
+      </c>
+      <c r="E52" s="3">
         <v>71100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>64700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>61000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>62100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>65600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>69400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>68300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>79300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>76500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>76700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>76000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>76500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>77000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>76600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>78600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>87500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>90500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>88300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>78200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>79200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>79600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>76000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>72100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4700</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>6100</v>
       </c>
       <c r="AC52" s="3">
         <v>6100</v>
       </c>
       <c r="AD52" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AE52" s="3">
         <v>5700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>24300</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4424,97 +4546,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>720000</v>
+      </c>
+      <c r="E54" s="3">
         <v>737700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>772700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>840900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>850900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>900600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>934900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>987300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>990700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>994600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>984800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1045400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1031500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1021700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1013900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1048000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1030000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1021300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1039000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1036200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1032000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1027100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1019200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1057100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>961400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>976000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>976500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>995100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>985800</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4546,8 +4674,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4579,97 +4708,101 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E57" s="3">
         <v>11200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>20900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>22900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>15400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>20900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>19700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>26600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>18700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>20400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>19200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>25200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>16200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>23400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>21400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>19500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>23300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>23900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>23800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>25600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>19900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>23200</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4757,186 +4890,195 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>187100</v>
+      </c>
+      <c r="E59" s="3">
         <v>196800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>193100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>226700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>202200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>215600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>218100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>251400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>249500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>244400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>226400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>277600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>261700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>253900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>240000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>274700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>240700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>227000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>225500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>244400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>220200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>217100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>199800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>219300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>187200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>190100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>173400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>179600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>163700</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>198800</v>
+      </c>
+      <c r="E60" s="3">
         <v>208000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>207800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>245600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>221900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>236500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>241000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>266500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>262600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>259900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>243900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>294300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>282600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>273600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>266600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>293400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>261100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>246200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>250600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>260500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>243500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>238600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>219300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>242600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>211200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>213900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>198900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>199500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>186900</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5024,97 +5166,103 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E62" s="3">
         <v>25200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>35200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>37300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>43100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>56500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>68600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>72800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>75800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>77200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>79900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>83200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>81700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>82600</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>87800</v>
       </c>
       <c r="R62" s="3">
         <v>87800</v>
       </c>
       <c r="S62" s="3">
+        <v>87800</v>
+      </c>
+      <c r="T62" s="3">
         <v>101900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>106800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>107600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>82900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>76500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>76300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>81500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>83400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>86700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>89600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>97300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>104100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5202,8 +5350,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5291,8 +5442,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5380,97 +5534,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>222200</v>
+      </c>
+      <c r="E66" s="3">
         <v>233200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>243000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>282900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>265000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>293000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>309600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>339200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>338400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>337100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>323800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>377600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>364300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>356200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>354400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>381200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>363000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>353000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>358300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>343500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>320100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>314900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>300800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>326000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>297900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>303600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>296200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>303700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>290600</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5502,8 +5662,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5591,8 +5752,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5680,8 +5844,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5769,8 +5936,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5858,97 +6028,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-461900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-447500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-415100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-384100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-344100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-315900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-291200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-269600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-260800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-248000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-236200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-229800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-220300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-216700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-215500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-207900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-202700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-194800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-184500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-176300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-164500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-160800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-151000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-137200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-198800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-187200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-175100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-160900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-154000</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6036,8 +6212,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6125,8 +6304,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6214,97 +6396,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>497700</v>
+      </c>
+      <c r="E76" s="3">
         <v>504500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>529700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>558000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>585900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>607600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>625300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>648100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>652300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>657500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>661000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>667800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>667100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>665600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>659500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>666900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>667000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>668300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>680700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>692700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>711900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>712300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>718400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>731100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>663500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>672400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>680300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>691400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>695200</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6392,191 +6580,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45233</v>
+      </c>
+      <c r="E80" s="2">
         <v>45142</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45051</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44960</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44862</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44771</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44680</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44589</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44498</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44407</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44225</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44134</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43952</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43770</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43679</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43588</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43497</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43406</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43315</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43224</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43133</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43042</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42951</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42860</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42769</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-14400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-32400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-31000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-40000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-28100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-24700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-21600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-8800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-6400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-10300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-11800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-13800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>22500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-9400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-10300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-13300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-6800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6608,97 +6805,101 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>9000</v>
+        <v>8100</v>
       </c>
       <c r="E83" s="3">
         <v>9000</v>
       </c>
       <c r="F83" s="3">
+        <v>9000</v>
+      </c>
+      <c r="G83" s="3">
         <v>8900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>10600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>10100</v>
-      </c>
-      <c r="L83" s="3">
-        <v>9900</v>
       </c>
       <c r="M83" s="3">
         <v>9900</v>
       </c>
       <c r="N83" s="3">
+        <v>9900</v>
+      </c>
+      <c r="O83" s="3">
         <v>10600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>10400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>10500</v>
-      </c>
-      <c r="R83" s="3">
-        <v>10900</v>
       </c>
       <c r="S83" s="3">
         <v>10900</v>
       </c>
       <c r="T83" s="3">
+        <v>10900</v>
+      </c>
+      <c r="U83" s="3">
         <v>10800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>10400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>10300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>10400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>10200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>10300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>10900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>10700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>10400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>10300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>10200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6786,8 +6987,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6875,8 +7079,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6964,8 +7171,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7053,8 +7263,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7142,97 +7355,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-27800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-42200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-26800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-16500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-24900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>18500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>11500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>17300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-30600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>32200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>22400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>26400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-20300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>43000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>22600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>16300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>31200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>15200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>29300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-18400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>5200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>11200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-19700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>11800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7264,97 +7483,101 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7442,8 +7665,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7531,97 +7757,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-7000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7653,8 +7885,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7742,8 +7975,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7831,8 +8067,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7920,8 +8159,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8009,80 +8251,83 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5100</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-400</v>
       </c>
       <c r="G100" s="3">
         <v>-400</v>
       </c>
       <c r="H100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I100" s="3">
         <v>-600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-6800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-8400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-14100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -8090,16 +8335,19 @@
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8187,93 +8435,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-29600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-49000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-28500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-18700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-34400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>15500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>16400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-39700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>32300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>25500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-25800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>43100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>21100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>6500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-18400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>13800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>12500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>26000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-24200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>6200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-25000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>5800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCWX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCWX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
   <si>
     <t>SCWX</t>
   </si>
@@ -656,417 +656,443 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45415</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45324</v>
+      </c>
+      <c r="F7" s="2">
         <v>45233</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45142</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45051</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44960</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44862</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44771</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44680</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44589</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44498</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44407</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44225</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44134</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43952</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43770</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43679</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43588</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43497</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43406</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43315</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43224</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43133</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43042</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42951</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42860</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42769</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>85700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>89200</v>
+      </c>
+      <c r="F8" s="3">
         <v>89400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>93000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>94400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>115300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>110900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>116200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>121000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>127900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>133700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>134200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>139500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>139700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>141600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>138500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>141200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>142000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>141300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>136600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>132800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>130700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>133100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>128800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>126200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>120900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>117100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>116200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>113700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>118900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>107100</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E9" s="3">
+        <v>30700</v>
+      </c>
+      <c r="F9" s="3">
         <v>34600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>40100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>42800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>46500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>45600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>49600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>49400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>50500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>52900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>56500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>57200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>59700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>59600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>59900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>62900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>64800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>61600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>63600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>62800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>60900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>62100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>62500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>60500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>60500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>55300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>55900</v>
-      </c>
-      <c r="AD9" s="3">
-        <v>53600</v>
-      </c>
-      <c r="AE9" s="3">
-        <v>56200</v>
       </c>
       <c r="AF9" s="3">
         <v>53600</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3">
+        <v>56200</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>53600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>57800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>58500</v>
+      </c>
+      <c r="F10" s="3">
         <v>54800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>52900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>51600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>68800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>65300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>66600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>71600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>77400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>80800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>77700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>82300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>80000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>82000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>78600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>78300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>77200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>79700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>73000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>70000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>69800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>71000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>66300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>65700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>60400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>61800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>60300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>60100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>62700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>53500</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1099,100 +1125,108 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>25200</v>
+      </c>
+      <c r="F12" s="3">
         <v>26400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>28200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>31200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>37600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>35300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>33600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>33300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>31200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>32800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>30400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>28200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>29200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>27600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>24100</v>
-      </c>
-      <c r="R12" s="3">
-        <v>24100</v>
-      </c>
-      <c r="S12" s="3">
-        <v>23400</v>
       </c>
       <c r="T12" s="3">
         <v>24100</v>
       </c>
       <c r="U12" s="3">
+        <v>23400</v>
+      </c>
+      <c r="V12" s="3">
+        <v>24100</v>
+      </c>
+      <c r="W12" s="3">
         <v>24900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>22600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>21700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>21100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>22500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>22400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>43000</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>19500</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>19700</v>
       </c>
       <c r="AD12" s="3">
         <v>19500</v>
       </c>
       <c r="AE12" s="3">
+        <v>19700</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>19500</v>
+      </c>
+      <c r="AG12" s="3">
         <v>32400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1283,28 +1317,34 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>14200</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" s="3">
-        <v>15500</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>24</v>
+      <c r="I14" s="3">
+        <v>20900</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>24</v>
@@ -1318,11 +1358,11 @@
       <c r="M14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1375,8 +1415,14 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1467,8 +1513,14 @@
       <c r="AF15" s="3">
         <v>3500</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1498,192 +1550,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>96300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>104400</v>
+      </c>
+      <c r="F17" s="3">
         <v>108600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>134100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>130700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>168800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>146900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>148400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>147400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>143100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>149100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>148100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>147300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>153900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>146500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>141400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>152000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>154500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>151500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>151700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>147300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>141100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>139600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>142900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>143800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>141300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>131800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>132200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>132700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>131000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-19200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-41100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-36300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-53500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-36000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-32200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-26400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-15200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-15400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-13900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-7800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-14200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-2900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-10800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-12500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-10200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-15100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-14500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-10400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-14100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-17600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-20400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-14700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-16000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-19000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-12100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-14900</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1716,192 +1782,206 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-1800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-1200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>2000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>1000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>1000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-10500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-32800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-29100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-42000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-27500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-23000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-17700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-5900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-6100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-4600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-3500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>5100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>7500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-1700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-2300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-3800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>4900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-5900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-9400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1992,192 +2072,210 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-18600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-41800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-38100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-50900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-36700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-32100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-27100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-16500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-16100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-14500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-8800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-14100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-9800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-12600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-11400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-13100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-14200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-10200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-5500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-13200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-17100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-22100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-14600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-16400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-19600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-11900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-13700</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="F24" s="3">
         <v>-4100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-9400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-7100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-10900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-8500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-7400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-5500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-7700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-3300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-2700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-2400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-4600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-1700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-2200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-7400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-3500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-2800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-5900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>1600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-17700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>-6400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-5100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2268,192 +2366,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-14400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-32400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-31000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-40000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-28100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-24700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-21600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-8800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-12900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-11800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-6400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-9500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-1200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-7500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-5200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-7900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-10300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-8300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-11800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-9800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-9400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-10300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-13300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-6800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-14400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-32400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-31000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-40000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-28100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-24700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-21600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-8800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-12900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-11800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-6400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-9500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-1200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-7500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-5200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-7900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-10300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-8300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-11800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-9800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-9400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-10300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-13300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-6800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2544,8 +2660,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2597,35 +2719,35 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>24</v>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-400</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>27000</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>24</v>
@@ -2636,8 +2758,14 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2728,8 +2856,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2820,192 +2954,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>1800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>1200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-2000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>1800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-14400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-32400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-31000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-40000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-28100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-24700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-21600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-8800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-12900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-11800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-6400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-9500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-7500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-5200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-7900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-10300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-8300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-11800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-9800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-13800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>22500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-9400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-10300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-13300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-6800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3096,197 +3248,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-14400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-32400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-31000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-40000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-28100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-24700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-21600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-8800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-12900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-11800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-6400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-9500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-7500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-5200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-7900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-10300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-8300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-11800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-9800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-13800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>22500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-9400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-10300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-13300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-6800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45415</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45324</v>
+      </c>
+      <c r="F38" s="2">
         <v>45233</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45142</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45051</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44960</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44862</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44771</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44680</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44589</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44498</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44407</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44225</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44134</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43952</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43770</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43679</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43588</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43497</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43406</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43315</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43224</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43133</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43042</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42951</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42860</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42769</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3319,8 +3489,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3353,100 +3525,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>68700</v>
+      </c>
+      <c r="F41" s="3">
         <v>58100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>64900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>94500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>143500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>139000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>167500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>186200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>220700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>205100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>197000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>180600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>220300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>188000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>181500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>156000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>181800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>138800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>117700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>111200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>129600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>115800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>103300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>77300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>101500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>99700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>97800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>91600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>116600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>110800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3537,135 +3717,147 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>54300</v>
+      </c>
+      <c r="F43" s="3">
         <v>55900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>56400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>57000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>72600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>64100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>71300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>74900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>86200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>95100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>97800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>94900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>108000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>107900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>108400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>116800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>111800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>118400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>120100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>135300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>141300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>134400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>133300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>146800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>157800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>136600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>122700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>123200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>113500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>700</v>
+      </c>
+      <c r="F44" s="3">
         <v>800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>800</v>
-      </c>
-      <c r="F44" s="3">
-        <v>700</v>
-      </c>
-      <c r="G44" s="3">
-        <v>600</v>
       </c>
       <c r="H44" s="3">
         <v>700</v>
       </c>
       <c r="I44" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="J44" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="K44" s="3">
         <v>500</v>
       </c>
       <c r="L44" s="3">
+        <v>400</v>
+      </c>
+      <c r="M44" s="3">
         <v>500</v>
       </c>
-      <c r="M44" s="3">
-        <v>600</v>
-      </c>
       <c r="N44" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="O44" s="3">
         <v>600</v>
@@ -3674,239 +3866,257 @@
         <v>700</v>
       </c>
       <c r="Q44" s="3">
+        <v>600</v>
+      </c>
+      <c r="R44" s="3">
         <v>700</v>
-      </c>
-      <c r="R44" s="3">
-        <v>800</v>
       </c>
       <c r="S44" s="3">
         <v>700</v>
       </c>
       <c r="T44" s="3">
+        <v>800</v>
+      </c>
+      <c r="U44" s="3">
+        <v>700</v>
+      </c>
+      <c r="V44" s="3">
         <v>900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>1100</v>
-      </c>
-      <c r="V44" s="3">
-        <v>600</v>
-      </c>
-      <c r="W44" s="3">
-        <v>500</v>
       </c>
       <c r="X44" s="3">
         <v>600</v>
       </c>
       <c r="Y44" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z44" s="3">
         <v>600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB44" s="3">
         <v>700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>1000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>1000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>1200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>1500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>1900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>14500</v>
+      </c>
+      <c r="F45" s="3">
         <v>12900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>17400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>17500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>17500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>26200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>27300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>27100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>26000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>14500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>17100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>16900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>17300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>26000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>28100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>27400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>27400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>26200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>24600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>24900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>27600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>41100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>40800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>42100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>40600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>27800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>51000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>51500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>47800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>111600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>138100</v>
+      </c>
+      <c r="F46" s="3">
         <v>127600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>139500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>169700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>234300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>229900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>266600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>288600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>333400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>315300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>312600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>293100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>346200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>322600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>318700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>301000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>321800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>284300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>263500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>271900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>299000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>291900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>278100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>266900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>300900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>265100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>272600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>267700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>279800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>248500</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3997,192 +4207,210 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F48" s="3">
         <v>7900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>9000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>13500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>13900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>19700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>21400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>23400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>25900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>30000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>33200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>36500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>39500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>42100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>43600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>46700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>51100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>54600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>58200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>62800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>36000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>31100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>32600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>32500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>66900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>34000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>32800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>31200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>62300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>27600</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>505000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>508700</v>
+      </c>
+      <c r="F49" s="3">
         <v>512200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>518100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>524800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>531700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>539100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>547000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>553500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>559700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>566100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>572300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>578500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>583700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>590200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>582400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>589600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>596500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>603600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>609100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>616000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>622900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>629900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>636800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>643700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>650700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>657600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>664500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>671500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>678400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>685300</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4273,8 +4501,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4365,100 +4599,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>44800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>70700</v>
+      </c>
+      <c r="F52" s="3">
         <v>72200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>71100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>64700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>61000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>62100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>65600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>69400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>68300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>79300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>76500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>76700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>76000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>76500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>77000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>76600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>78600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>87500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>90500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>88300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>78200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>79200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>79600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>76000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>72100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>4700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>6100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>6100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>5700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>24300</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4549,100 +4795,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>667900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>724800</v>
+      </c>
+      <c r="F54" s="3">
         <v>720000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>737700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>772700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>840900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>850900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>900600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>934900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>987300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>990700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>994600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>984800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1045400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1031500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1021700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1013900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1048000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1030000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1021300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1039000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1036200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1032000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1027100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1019200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1057100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>961400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>976000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>976500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>995100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>985800</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4675,8 +4933,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4709,100 +4969,108 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F57" s="3">
         <v>11700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>11200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>14800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>18800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>19700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>20900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>22900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>15100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>13100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>15400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>17500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>16800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>20900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>19700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>26600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>18700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>20400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>19200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>25200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>16200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>23400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>21400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>19500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>23300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>23900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>23800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>25600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>19900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>23200</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4893,192 +5161,210 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>170400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>193100</v>
+      </c>
+      <c r="F59" s="3">
         <v>187100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>196800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>193100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>226700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>202200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>215600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>218100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>251400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>249500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>244400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>226400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>277600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>261700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>253900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>240000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>274700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>240700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>227000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>225500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>244400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>220200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>217100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>199800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>219300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>187200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>190100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>173400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>179600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>163700</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>181300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>202100</v>
+      </c>
+      <c r="F60" s="3">
         <v>198800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>208000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>207800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>245600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>221900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>236500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>241000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>266500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>262600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>259900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>243900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>294300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>282600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>273600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>266600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>293400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>261100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>246200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>250600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>260500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>243500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>238600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>219300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>242600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>211200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>213900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>198900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>199500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>186900</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5169,100 +5455,112 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>21300</v>
+      </c>
+      <c r="F62" s="3">
         <v>23500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>25200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>35200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>37300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>43100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>56500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>68600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>72800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>75800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>77200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>79900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>83200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>81700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>82600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>87800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>87800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>101900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>106800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>107600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>82900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>76500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>76300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>81500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>83400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>86700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>89600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>97300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>104100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5353,8 +5651,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5445,8 +5749,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5537,100 +5847,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>200600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>223500</v>
+      </c>
+      <c r="F66" s="3">
         <v>222200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>233200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>243000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>282900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>265000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>293000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>309600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>339200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>338400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>337100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>323800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>377600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>364300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>356200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>354400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>381200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>363000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>353000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>358300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>343500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>320100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>314900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>300800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>326000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>297900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>303600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>296200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>303700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>290600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5663,8 +5985,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5755,8 +6079,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5847,8 +6177,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5939,8 +6275,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6031,100 +6373,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-506200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-470200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-461900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-447500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-415100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-384100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-344100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-315900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-291200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-269600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-260800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-248000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-236200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-229800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-220300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-216700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-215500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-207900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-202700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-194800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-184500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-176300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-164500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-160800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-137200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-198800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-187200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-175100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-160900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-154000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6215,8 +6569,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6307,8 +6667,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6399,100 +6765,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>467200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>501300</v>
+      </c>
+      <c r="F76" s="3">
         <v>497700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>504500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>529700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>558000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>585900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>607600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>625300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>648100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>652300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>657500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>661000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>667800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>667100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>665600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>659500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>666900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>667000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>668300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>680700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>692700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>711900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>712300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>718400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>731100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>663500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>672400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>680300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>691400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>695200</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6583,197 +6961,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45415</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45324</v>
+      </c>
+      <c r="F80" s="2">
         <v>45233</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45142</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45051</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44960</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44862</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44771</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44680</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44589</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44498</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44407</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44225</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44134</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43952</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43770</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43679</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43588</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43497</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43406</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43315</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43224</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43133</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43042</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42951</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42860</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42769</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-14400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-32400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-31000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-40000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-28100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-24700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-21600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-8800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-12900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-11800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-6400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-9500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-7500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-5200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-7900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-10300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-8300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-11800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-9800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-13800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>22500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-9400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-10300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-13300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-6800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6806,100 +7202,108 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F83" s="3">
         <v>8100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>9000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>9000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>8900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>9200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>9100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>9400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>10600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>10100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>9900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>9900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>10600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>10100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>10400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>10500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>10900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>10900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>10800</v>
-      </c>
-      <c r="V83" s="3">
-        <v>10400</v>
-      </c>
-      <c r="W83" s="3">
-        <v>10300</v>
       </c>
       <c r="X83" s="3">
         <v>10400</v>
       </c>
       <c r="Y83" s="3">
+        <v>10300</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>10400</v>
+      </c>
+      <c r="AA83" s="3">
         <v>10200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>10300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>10900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>10700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>10400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>10300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>10200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6990,8 +7394,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7082,8 +7492,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7174,8 +7590,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7266,8 +7688,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7358,100 +7786,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-12600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>15300</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-27800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-42200</v>
       </c>
-      <c r="G89" s="3">
-        <v>5600</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
+        <v>9400</v>
+      </c>
+      <c r="J89" s="3">
         <v>-26800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-16500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-24900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>18500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>11500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>17300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-30600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>32200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>22400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>26400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-20300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>43000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>22600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>16300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-3000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>31200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>15200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>29300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-18400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>4000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>5200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>11200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-19700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>11800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7484,100 +7924,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-1300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-1700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="P91" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="R91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-800</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="T91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
-        <v>-700</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-500</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-1400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-3600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-7000</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-1600</v>
       </c>
       <c r="Y91" s="3">
         <v>-3200</v>
       </c>
       <c r="Z91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-6700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7668,8 +8116,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7760,100 +8214,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-1300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-1700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-1300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-2200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-1600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-2000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-2300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-15600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-1000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-1400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-3600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-7000</v>
-      </c>
-      <c r="W94" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="X94" s="3">
-        <v>-1600</v>
       </c>
       <c r="Y94" s="3">
         <v>-3200</v>
       </c>
       <c r="Z94" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AA94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-6100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7886,8 +8352,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7978,8 +8446,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8070,8 +8544,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8162,8 +8642,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8254,123 +8740,135 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G100" s="3">
         <v>-600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-5100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-7400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-1800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>1000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-6800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-4500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-6100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-8400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-14100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+        <v>-1100</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -8438,96 +8936,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-6800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-29600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-49000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>4500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-28500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-18700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-34400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>15500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>8200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>16400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-39700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>32300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>6600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>25500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-25800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>43100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>21100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>6500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-18400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>13800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>12500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>26000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-24200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>1800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>1900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>6200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-25000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>5800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-2400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCWX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCWX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>SCWX</t>
   </si>
@@ -656,443 +656,456 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45506</v>
+      </c>
+      <c r="E7" s="2">
         <v>45415</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45324</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45233</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45142</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45051</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44960</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44862</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44771</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44680</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44589</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44498</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44407</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44225</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44134</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44043</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43952</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43861</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43770</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43679</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43588</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43497</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43406</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43315</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43224</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43133</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43042</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42951</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42860</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42769</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>82200</v>
+      </c>
+      <c r="E8" s="3">
         <v>85700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>89200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>89400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>93000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>94400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>115300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>110900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>116200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>121000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>127900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>133700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>134200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>139500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>139700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>141600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>138500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>141200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>142000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>141300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>136600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>132800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>130700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>133100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>128800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>126200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>120900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>117100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>116200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>113700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>118900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>107100</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E9" s="3">
         <v>27900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>30700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>34600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>40100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>42800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>46500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>45600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>49600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>49400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>50500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>52900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>56500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>57200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>59700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>59600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>59900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>62900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>64800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>61600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>63600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>62800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>60900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>62100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>62500</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>60500</v>
       </c>
       <c r="AC9" s="3">
         <v>60500</v>
       </c>
       <c r="AD9" s="3">
+        <v>60500</v>
+      </c>
+      <c r="AE9" s="3">
         <v>55300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>55900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>53600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>56200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>54800</v>
+      </c>
+      <c r="E10" s="3">
         <v>57800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>58500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>54800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>52900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>51600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>68800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>65300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>66600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>71600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>77400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>80800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>77700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>82300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>80000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>82000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>78600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>78300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>77200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>79700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>73000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>70000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>69800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>71000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>66300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>65700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>60400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>61800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>60300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>60100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>62700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>53500</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1127,106 +1140,110 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>22800</v>
+      </c>
+      <c r="E12" s="3">
         <v>24500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>25200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>26400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>28200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>31200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>37600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>35300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>33600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>33300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>31200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>32800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>30400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>28200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>29200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>27600</v>
-      </c>
-      <c r="S12" s="3">
-        <v>24100</v>
       </c>
       <c r="T12" s="3">
         <v>24100</v>
       </c>
       <c r="U12" s="3">
+        <v>24100</v>
+      </c>
+      <c r="V12" s="3">
         <v>23400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>24100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>24900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>22600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>21700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>21100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>22500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>22400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>43000</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>19500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>19700</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>19500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>32400</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1323,31 +1340,34 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>1500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2900</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>14200</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>20900</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>24</v>
@@ -1364,8 +1384,8 @@
       <c r="O14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1421,8 +1441,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1519,8 +1542,11 @@
       <c r="AH15" s="3">
         <v>3500</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1552,204 +1578,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>95300</v>
+      </c>
+      <c r="E17" s="3">
         <v>96300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>104400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>108600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>134100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>130700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>168800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>146900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>148400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>147400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>143100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>149100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>148100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>147300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>153900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>146500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>141400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>152000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>154500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>151500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>151700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>147300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>141100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>139600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>142900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>143800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>141300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>131800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>132200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>132700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>131000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-15200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-19200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-41100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-36300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-53500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-36000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-32200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-26400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-15200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-15400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-13900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-14200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-4900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-12500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-10200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-15100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-14500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-10400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-14100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-17600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-20400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-14700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-16000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-19000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-12100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-14900</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1784,204 +1817,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E20" s="3">
         <v>700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>1000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>200</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>1000</v>
       </c>
       <c r="AA20" s="3">
         <v>1000</v>
       </c>
       <c r="AB20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC20" s="3">
         <v>500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-8500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-4000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-10200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-10500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-32800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-29100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-42000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-27500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-23000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-6100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>7500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-6800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-9400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2078,204 +2118,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-18600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-41800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-38100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-50900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-36700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-32100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-27100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-16500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-14500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-14100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-12600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-13100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-14200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-13200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-17100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-22100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-14600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-16400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-19600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-11900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-13700</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>700</v>
+      </c>
+      <c r="E24" s="3">
         <v>26200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-7800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-4100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-9400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-7100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-10900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-8500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-7400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-5500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-7700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-4600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-2200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-7400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-3500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-2800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-17700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-5200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-6100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-6400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-5100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2372,204 +2421,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-36100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-14400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-32400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-31000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-40000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-28100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-24700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-21600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-8800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-11800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-7500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-10300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-13400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-9400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-10300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-13300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-6800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-36100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-14400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-32400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-31000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-40000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-28100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-24700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-21600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-8800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-11800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-7500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-10300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-13400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-9400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-10300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-13300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-6800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2666,8 +2724,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2786,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>24</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>24</v>
@@ -2734,8 +2795,8 @@
       <c r="X29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
@@ -2744,13 +2805,13 @@
         <v>0</v>
       </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-400</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>27000</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
@@ -2764,8 +2825,11 @@
       <c r="AH29" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2862,8 +2926,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2960,204 +3027,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-1000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-200</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AA32" s="3">
         <v>-1000</v>
       </c>
       <c r="AB32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-36100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-14400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-32400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-31000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-40000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-28100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-24700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-21600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-8800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-11800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-7500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-10300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-13800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>22500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-9400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-10300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-13300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-6800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3254,209 +3330,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-36100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-14400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-32400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-31000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-40000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-28100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-24700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-21600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-8800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-11800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-7500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-10300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-13800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>22500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-9400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-10300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-13300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-6800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45506</v>
+      </c>
+      <c r="E38" s="2">
         <v>45415</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45324</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45233</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45142</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45051</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44960</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44862</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44771</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44680</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44589</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44498</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44407</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44225</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44134</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44043</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43952</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43861</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43770</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43679</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43588</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43497</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43406</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43315</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43224</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43133</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43042</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42951</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42860</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42769</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3491,8 +3576,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3527,106 +3613,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E41" s="3">
         <v>47000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>68700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>58100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>64900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>94500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>143500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>139000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>167500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>186200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>220700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>205100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>197000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>180600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>220300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>188000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>181500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>156000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>181800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>138800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>117700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>111200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>129600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>115800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>103300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>77300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>101500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>99700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>97800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>91600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>116600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>110800</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3723,204 +3813,213 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>50700</v>
+      </c>
+      <c r="E43" s="3">
         <v>46800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>54300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>55900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>56400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>57000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>72600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>64100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>71300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>74900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>86200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>95100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>97800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>94900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>108000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>107900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>108400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>116800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>111800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>118400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>120100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>135300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>141300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>134400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>133300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>146800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>157800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>136600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>122700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>123200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>113500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="3">
         <v>1100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>700</v>
-      </c>
-      <c r="F44" s="3">
-        <v>800</v>
       </c>
       <c r="G44" s="3">
         <v>800</v>
       </c>
       <c r="H44" s="3">
+        <v>800</v>
+      </c>
+      <c r="I44" s="3">
         <v>700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>400</v>
-      </c>
-      <c r="M44" s="3">
-        <v>500</v>
       </c>
       <c r="N44" s="3">
         <v>500</v>
       </c>
       <c r="O44" s="3">
+        <v>500</v>
+      </c>
+      <c r="P44" s="3">
         <v>600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>600</v>
-      </c>
-      <c r="R44" s="3">
-        <v>700</v>
       </c>
       <c r="S44" s="3">
         <v>700</v>
       </c>
       <c r="T44" s="3">
+        <v>700</v>
+      </c>
+      <c r="U44" s="3">
         <v>800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>500</v>
-      </c>
-      <c r="Z44" s="3">
-        <v>600</v>
       </c>
       <c r="AA44" s="3">
         <v>600</v>
       </c>
       <c r="AB44" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC44" s="3">
         <v>700</v>
-      </c>
-      <c r="AC44" s="3">
-        <v>1000</v>
       </c>
       <c r="AD44" s="3">
         <v>1000</v>
       </c>
       <c r="AE44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AF44" s="3">
         <v>1200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3928,195 +4027,201 @@
         <v>16600</v>
       </c>
       <c r="E45" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F45" s="3">
         <v>14500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>17400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>17500</v>
       </c>
       <c r="I45" s="3">
         <v>17500</v>
       </c>
       <c r="J45" s="3">
+        <v>17500</v>
+      </c>
+      <c r="K45" s="3">
         <v>26200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>27300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>27100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>26000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>16900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>26000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>28100</v>
-      </c>
-      <c r="T45" s="3">
-        <v>27400</v>
       </c>
       <c r="U45" s="3">
         <v>27400</v>
       </c>
       <c r="V45" s="3">
+        <v>27400</v>
+      </c>
+      <c r="W45" s="3">
         <v>26200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>24600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>24900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>27600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>41100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>40800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>42100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>40600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>27800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>51000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>51500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>47800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>114900</v>
+      </c>
+      <c r="E46" s="3">
         <v>111600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>138100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>127600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>139500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>169700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>234300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>229900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>266600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>288600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>333400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>315300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>312600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>293100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>346200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>322600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>318700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>301000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>321800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>284300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>263500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>271900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>299000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>291900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>278100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>266900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>300900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>265100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>272600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>267700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>279800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>248500</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4213,204 +4318,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E48" s="3">
         <v>6500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>23400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>30000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>33200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>36500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>39500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>42100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>43600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>46700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>51100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>54600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>58200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>62800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>36000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>31100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>32600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>32500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>66900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>34000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>32800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>31200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>62300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>27600</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>501500</v>
+      </c>
+      <c r="E49" s="3">
         <v>505000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>508700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>512200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>518100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>524800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>531700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>539100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>547000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>553500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>559700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>566100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>572300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>578500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>583700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>590200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>582400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>589600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>596500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>603600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>609100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>616000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>622900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>629900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>636800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>643700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>650700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>657600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>664500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>671500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>678400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>685300</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4507,8 +4621,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4605,106 +4722,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>43400</v>
+      </c>
+      <c r="E52" s="3">
         <v>44800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>70700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>72200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>71100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>64700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>61000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>62100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>65600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>69400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>68300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>79300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>76500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>76700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>76000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>76500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>77000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>76600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>78600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>87500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>90500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>88300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>78200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>79200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>79600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>76000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>72100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>4700</v>
-      </c>
-      <c r="AE52" s="3">
-        <v>6100</v>
       </c>
       <c r="AF52" s="3">
         <v>6100</v>
       </c>
       <c r="AG52" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AH52" s="3">
         <v>5700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>24300</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4801,106 +4924,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>665500</v>
+      </c>
+      <c r="E54" s="3">
         <v>667900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>724800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>720000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>737700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>772700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>840900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>850900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>900600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>934900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>987300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>990700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>994600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>984800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1045400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1031500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1021700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1013900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1048000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1030000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1021300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1039000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1036200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1032000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1027100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1019200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1057100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>961400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>976000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>976500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>995100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>985800</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4935,8 +5064,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4971,106 +5101,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E57" s="3">
         <v>10900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>19700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>20900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>22900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>15100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>15400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>20900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>19700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>26600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>18700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>20400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>19200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>25200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>16200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>23400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>21400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>19500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>23300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>23900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>23800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>25600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>19900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>23200</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5167,204 +5301,213 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>173000</v>
+      </c>
+      <c r="E59" s="3">
         <v>170400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>193100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>187100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>196800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>193100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>226700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>202200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>215600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>218100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>251400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>249500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>244400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>226400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>277600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>261700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>253900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>240000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>274700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>240700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>227000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>225500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>244400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>220200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>217100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>199800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>219300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>187200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>190100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>173400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>179600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>163700</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>181700</v>
+      </c>
+      <c r="E60" s="3">
         <v>181300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>202100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>198800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>208000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>207800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>245600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>221900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>236500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>241000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>266500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>262600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>259900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>243900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>294300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>282600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>273600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>266600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>293400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>261100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>246200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>250600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>260500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>243500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>238600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>219300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>242600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>211200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>213900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>198900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>199500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>186900</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5461,106 +5604,112 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E62" s="3">
         <v>19300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>21300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>25200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>35200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>37300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>43100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>56500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>68600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>72800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>75800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>77200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>79900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>83200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>81700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>82600</v>
-      </c>
-      <c r="T62" s="3">
-        <v>87800</v>
       </c>
       <c r="U62" s="3">
         <v>87800</v>
       </c>
       <c r="V62" s="3">
+        <v>87800</v>
+      </c>
+      <c r="W62" s="3">
         <v>101900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>106800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>107600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>82900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>76500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>76300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>81500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>83400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>86700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>89600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>97300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>104100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5657,8 +5806,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5755,8 +5907,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5853,106 +6008,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>205100</v>
+      </c>
+      <c r="E66" s="3">
         <v>200600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>223500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>222200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>233200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>243000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>282900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>265000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>293000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>309600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>339200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>338400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>337100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>323800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>377600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>364300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>356200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>354400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>381200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>363000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>353000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>358300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>343500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>320100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>314900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>300800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>326000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>297900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>303600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>296200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>303700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>290600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5987,8 +6148,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6085,8 +6247,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6183,8 +6348,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6281,8 +6449,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6379,106 +6550,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-521000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-506200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-470200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-461900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-447500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-415100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-384100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-344100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-315900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-291200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-269600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-260800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-248000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-236200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-229800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-220300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-216700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-215500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-207900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-202700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-194800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-184500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-176300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-164500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-160800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-137200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-198800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-187200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-175100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-160900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-154000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6575,8 +6752,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6673,8 +6853,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6771,106 +6954,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>460400</v>
+      </c>
+      <c r="E76" s="3">
         <v>467200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>501300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>497700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>504500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>529700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>558000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>585900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>607600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>625300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>648100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>652300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>657500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>661000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>667800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>667100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>665600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>659500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>666900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>667000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>668300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>680700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>692700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>711900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>712300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>718400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>731100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>663500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>672400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>680300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>691400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>695200</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6967,209 +7156,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45506</v>
+      </c>
+      <c r="E80" s="2">
         <v>45415</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45324</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45233</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45142</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45051</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44960</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44862</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44771</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44680</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44589</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44498</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44407</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44225</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44134</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44043</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43952</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43861</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43770</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43679</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43588</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43497</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43406</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43315</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43224</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43133</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43042</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42951</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42860</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42769</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-36100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-14400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-32400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-31000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-40000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-28100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-24700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-21600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-8800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-11800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-7500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-10300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-13800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>22500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-9400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-10300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-13300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-6800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7204,106 +7402,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>5900</v>
+        <v>5500</v>
       </c>
       <c r="E83" s="3">
         <v>5900</v>
       </c>
       <c r="F83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="G83" s="3">
         <v>8100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>9000</v>
       </c>
       <c r="H83" s="3">
         <v>9000</v>
       </c>
       <c r="I83" s="3">
+        <v>9000</v>
+      </c>
+      <c r="J83" s="3">
         <v>8900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>10600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>10100</v>
-      </c>
-      <c r="O83" s="3">
-        <v>9900</v>
       </c>
       <c r="P83" s="3">
         <v>9900</v>
       </c>
       <c r="Q83" s="3">
+        <v>9900</v>
+      </c>
+      <c r="R83" s="3">
         <v>10600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>10100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>10400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>10500</v>
-      </c>
-      <c r="U83" s="3">
-        <v>10900</v>
       </c>
       <c r="V83" s="3">
         <v>10900</v>
       </c>
       <c r="W83" s="3">
+        <v>10900</v>
+      </c>
+      <c r="X83" s="3">
         <v>10800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>10400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>10300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>10400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>10200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>10300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>10900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>10700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>10400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>10300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>10200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7400,8 +7602,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7498,8 +7703,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7596,8 +7804,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7694,8 +7905,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7792,106 +8006,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-12600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>15300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-27800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-42200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-26800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-16500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-24900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>18500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>11500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>17300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-30600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>32200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>22400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>26400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-20300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>43000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>22600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>16300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>31200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>15200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>29300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-18400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>4000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>5200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>11200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-19700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>11800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7926,106 +8146,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-6700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8122,8 +8346,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8220,106 +8447,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-15600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-6100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8354,8 +8587,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8452,8 +8686,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8550,8 +8787,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8648,8 +8888,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8746,89 +8989,92 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-6000</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-200</v>
       </c>
       <c r="F100" s="3">
         <v>-200</v>
       </c>
       <c r="G100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H100" s="3">
         <v>-600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-5100</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-400</v>
       </c>
       <c r="J100" s="3">
         <v>-400</v>
       </c>
       <c r="K100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L100" s="3">
         <v>-600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-8400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-14100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
         <v>0</v>
       </c>
@@ -8836,24 +9082,27 @@
         <v>0</v>
       </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-2000</v>
       </c>
-      <c r="AG100" s="3">
-        <v>0</v>
-      </c>
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1100</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>24</v>
@@ -8870,8 +9119,8 @@
       <c r="J101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -8942,102 +9191,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-21600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-29600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-49000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-28500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-18700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-34400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>15500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>16400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-39700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>32300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>25500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-25800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>43100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>21100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>6500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-18400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>13800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>12500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>26000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-24200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>6200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-25000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>5800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SCWX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SCWX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>SCWX</t>
   </si>
@@ -656,456 +656,468 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45597</v>
+      </c>
+      <c r="E7" s="2">
         <v>45506</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45415</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45324</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45233</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45142</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45051</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44960</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44862</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44771</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44680</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44589</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44498</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44407</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44316</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44225</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44134</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44043</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43952</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43861</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43770</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43679</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43588</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43497</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43406</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43315</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43224</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43133</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43042</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42951</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42860</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42769</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>82700</v>
+      </c>
+      <c r="E8" s="3">
         <v>82200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>85700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>89200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>89400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>93000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>94400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>115300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>110900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>116200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>121000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>127900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>133700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>134200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>139500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>139700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>141600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>138500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>141200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>142000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>141300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>136600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>132800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>130700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>133100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>128800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>126200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>120900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>117100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>116200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>113700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>118900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>107100</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E9" s="3">
         <v>27400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>27900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>30700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>34600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>40100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>42800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>46500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>45600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>49600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>49400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>50500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>52900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>56500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>57200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>59700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>59600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>59900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>62900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>64800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>61600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>63600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>62800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>60900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>62100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>62500</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>60500</v>
       </c>
       <c r="AD9" s="3">
         <v>60500</v>
       </c>
       <c r="AE9" s="3">
+        <v>60500</v>
+      </c>
+      <c r="AF9" s="3">
         <v>55300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>55900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>53600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>56200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>54800</v>
+        <v>56100</v>
       </c>
       <c r="E10" s="3">
+        <v>54700</v>
+      </c>
+      <c r="F10" s="3">
         <v>57800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>58500</v>
       </c>
-      <c r="G10" s="3">
-        <v>54800</v>
-      </c>
       <c r="H10" s="3">
+        <v>54700</v>
+      </c>
+      <c r="I10" s="3">
         <v>52900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>51600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>68800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>65300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>66600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>71600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>77400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>80800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>77700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>82300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>80000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>82000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>78600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>78300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>77200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>79700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>73000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>70000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>69800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>71000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>66300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>65700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>60400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>61800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>60300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>60100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>62700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>53500</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1141,109 +1153,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E12" s="3">
         <v>22800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>24500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>25200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>26400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>28200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>31200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>37600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>35300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>33600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>33300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>31200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>32800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>30400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>28200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>29200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>27600</v>
-      </c>
-      <c r="T12" s="3">
-        <v>24100</v>
       </c>
       <c r="U12" s="3">
         <v>24100</v>
       </c>
       <c r="V12" s="3">
+        <v>24100</v>
+      </c>
+      <c r="W12" s="3">
         <v>23400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>24100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>24900</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>22600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>21700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>21100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>22500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>22400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>43000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>19500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>19700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>19500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>32400</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1343,34 +1359,37 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="3">
         <v>1500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2900</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="3">
         <v>14200</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>20900</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>24</v>
@@ -1387,8 +1406,8 @@
       <c r="P14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1444,31 +1463,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>3500</v>
+        <v>5700</v>
       </c>
       <c r="E15" s="3">
-        <v>3500</v>
+        <v>5500</v>
       </c>
       <c r="F15" s="3">
-        <v>3500</v>
+        <v>5900</v>
       </c>
       <c r="G15" s="3">
-        <v>3500</v>
+        <v>5900</v>
       </c>
       <c r="H15" s="3">
-        <v>3500</v>
+        <v>8100</v>
       </c>
       <c r="I15" s="3">
-        <v>3500</v>
+        <v>9000</v>
       </c>
       <c r="J15" s="3">
-        <v>3500</v>
+        <v>9000</v>
       </c>
       <c r="K15" s="3">
         <v>3500</v>
@@ -1545,8 +1567,11 @@
       <c r="AI15" s="3">
         <v>3500</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>3500</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1579,210 +1604,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>104900</v>
+      </c>
+      <c r="E17" s="3">
         <v>95300</v>
       </c>
-      <c r="E17" s="3">
-        <v>96300</v>
-      </c>
       <c r="F17" s="3">
-        <v>104400</v>
+        <v>94800</v>
       </c>
       <c r="G17" s="3">
+        <v>101400</v>
+      </c>
+      <c r="H17" s="3">
         <v>108600</v>
       </c>
-      <c r="H17" s="3">
-        <v>134100</v>
-      </c>
       <c r="I17" s="3">
+        <v>119900</v>
+      </c>
+      <c r="J17" s="3">
         <v>130700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>168800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>146900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>148400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>147400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>143100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>149100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>148100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>147300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>153900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>146500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>141400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>152000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>154500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>151500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>151700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>147300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>141100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>139600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>142900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>143800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>141300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>131800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>132200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>132700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>131000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>122000</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-22200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13100</v>
       </c>
-      <c r="E18" s="3">
-        <v>-10600</v>
-      </c>
       <c r="F18" s="3">
+        <v>-9200</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-36400</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-53500</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-36000</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-32200</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="O18" s="3">
         <v>-15200</v>
       </c>
-      <c r="G18" s="3">
-        <v>-19200</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-41100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-36300</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-53500</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-36000</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-32200</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-26400</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-15200</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-15400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-14200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-4900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-10800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-12500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-10200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-15100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-14500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-10400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-14100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-17600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-20400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-14700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-16000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-19000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-12100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-14900</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1818,233 +1850,240 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="R20" s="3">
         <v>-900</v>
       </c>
-      <c r="E20" s="3">
-        <v>700</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G20" s="3">
-        <v>600</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="J20" s="3">
-        <v>2500</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-600</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-800</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-600</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-900</v>
-      </c>
-      <c r="R20" s="3">
-        <v>100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>1000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>200</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>1000</v>
       </c>
       <c r="AB20" s="3">
         <v>1000</v>
       </c>
       <c r="AC20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AD20" s="3">
         <v>500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-8500</v>
+        <v>-16500</v>
       </c>
       <c r="E21" s="3">
-        <v>-4000</v>
+        <v>-7600</v>
       </c>
       <c r="F21" s="3">
-        <v>-10200</v>
+        <v>-3300</v>
       </c>
       <c r="G21" s="3">
-        <v>-10500</v>
+        <v>-9000</v>
       </c>
       <c r="H21" s="3">
-        <v>-32800</v>
+        <v>-11200</v>
       </c>
       <c r="I21" s="3">
-        <v>-29100</v>
+        <v>-17900</v>
       </c>
       <c r="J21" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="K21" s="3">
         <v>-42000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-27500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-23000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-17700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-6100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-6800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-11300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-5900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-9400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-3900</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
+        <v>900</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+        <v>-1700</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2121,210 +2160,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-14000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-16100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-18600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-41800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-38100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-50900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-36700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-32100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-27100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-14100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-12600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-13100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-14200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-10200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-5500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-13200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-17100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-22100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-14600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-16400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-19600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-11900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-13700</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E24" s="3">
         <v>700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>26200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-7800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-4100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-9400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-7100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-10900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-8500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-7400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-5500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-7700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-4600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-2200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-7400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-3500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-5900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-17700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-6400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-5100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2424,210 +2472,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-14700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-36100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-8300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-14400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-32400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-31000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-40000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-28100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-24700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-21600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-8800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-12900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-7900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-10300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-9800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-13400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-9400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-10300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-13300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-6800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-14700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-36100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-8300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-14400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-32400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-31000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-40000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-28100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-24700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-21600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-8800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-12900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-10300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-9800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-13400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-9400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-10300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-13300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-6800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -2727,8 +2784,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2789,8 +2849,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>24</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>24</v>
@@ -2798,8 +2858,8 @@
       <c r="Y29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
@@ -2808,13 +2868,13 @@
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-400</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>27000</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>24</v>
@@ -2828,8 +2888,11 @@
       <c r="AI29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2929,8 +2992,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3030,210 +3096,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="L32" s="3">
+        <v>600</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
+        <v>700</v>
+      </c>
+      <c r="O32" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P32" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>600</v>
+      </c>
+      <c r="R32" s="3">
         <v>900</v>
       </c>
-      <c r="E32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="F32" s="3">
-        <v>900</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="H32" s="3">
-        <v>700</v>
-      </c>
-      <c r="I32" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-2500</v>
-      </c>
-      <c r="K32" s="3">
-        <v>600</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>700</v>
-      </c>
-      <c r="N32" s="3">
-        <v>1300</v>
-      </c>
-      <c r="O32" s="3">
-        <v>800</v>
-      </c>
-      <c r="P32" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>900</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-1000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AB32" s="3">
         <v>-1000</v>
       </c>
       <c r="AC32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-14700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-36100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-8300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-14400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-32400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-31000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-40000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-28100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-24700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-21600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-8800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-12900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-10300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-9800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-13800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>22500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-9400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-10300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-13300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-6800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3333,215 +3408,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-14700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-36100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-8300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-14400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-32400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-31000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-40000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-28100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-24700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-21600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-8800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-12900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-10300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-9800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-13800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>22500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-9400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-10300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-13300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-6800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45597</v>
+      </c>
+      <c r="E38" s="2">
         <v>45506</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45415</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45324</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45233</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45142</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45051</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44960</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44862</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44771</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44680</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44589</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44498</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44407</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44316</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44225</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44134</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44043</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43952</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43861</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43770</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43679</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43588</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43497</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43406</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43315</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43224</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43133</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43042</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42951</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42860</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42769</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3577,8 +3661,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3614,109 +3699,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E41" s="3">
         <v>47600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>47000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>68700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>58100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>64900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>94500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>143500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>139000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>167500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>186200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>220700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>205100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>197000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>180600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>220300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>188000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>181500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>156000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>181800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>138800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>117700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>111200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>129600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>115800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>103300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>77300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>101500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>99700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>97800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>91600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>116600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>110800</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3816,435 +3905,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>53700</v>
+      </c>
+      <c r="E43" s="3">
         <v>50700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>46800</v>
       </c>
-      <c r="F43" s="3">
-        <v>54300</v>
-      </c>
       <c r="G43" s="3">
+        <v>59400</v>
+      </c>
+      <c r="H43" s="3">
         <v>55900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>56400</v>
       </c>
-      <c r="I43" s="3">
-        <v>57000</v>
-      </c>
       <c r="J43" s="3">
+        <v>66100</v>
+      </c>
+      <c r="K43" s="3">
         <v>72600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>64100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>71300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>74900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>86200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>95100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>97800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>94900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>108000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>107900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>108400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>116800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>111800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>118400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>120100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>135300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>141300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>134400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>133300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>146800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>157800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>136600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>122700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>123200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>113500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" s="3">
         <v>1100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>700</v>
-      </c>
-      <c r="G44" s="3">
-        <v>800</v>
       </c>
       <c r="H44" s="3">
         <v>800</v>
       </c>
       <c r="I44" s="3">
+        <v>800</v>
+      </c>
+      <c r="J44" s="3">
         <v>700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>400</v>
-      </c>
-      <c r="N44" s="3">
-        <v>500</v>
       </c>
       <c r="O44" s="3">
         <v>500</v>
       </c>
       <c r="P44" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q44" s="3">
         <v>600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>600</v>
-      </c>
-      <c r="S44" s="3">
-        <v>700</v>
       </c>
       <c r="T44" s="3">
         <v>700</v>
       </c>
       <c r="U44" s="3">
+        <v>700</v>
+      </c>
+      <c r="V44" s="3">
         <v>800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>500</v>
-      </c>
-      <c r="AA44" s="3">
-        <v>600</v>
       </c>
       <c r="AB44" s="3">
         <v>600</v>
       </c>
       <c r="AC44" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD44" s="3">
         <v>700</v>
-      </c>
-      <c r="AD44" s="3">
-        <v>1000</v>
       </c>
       <c r="AE44" s="3">
         <v>1000</v>
       </c>
       <c r="AF44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AG44" s="3">
         <v>1200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>16600</v>
+        <v>13400</v>
       </c>
       <c r="E45" s="3">
         <v>16600</v>
       </c>
       <c r="F45" s="3">
+        <v>16600</v>
+      </c>
+      <c r="G45" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H45" s="3">
+        <v>12900</v>
+      </c>
+      <c r="I45" s="3">
+        <v>17400</v>
+      </c>
+      <c r="J45" s="3">
+        <v>8500</v>
+      </c>
+      <c r="K45" s="3">
+        <v>17500</v>
+      </c>
+      <c r="L45" s="3">
+        <v>26200</v>
+      </c>
+      <c r="M45" s="3">
+        <v>27300</v>
+      </c>
+      <c r="N45" s="3">
+        <v>27100</v>
+      </c>
+      <c r="O45" s="3">
+        <v>26000</v>
+      </c>
+      <c r="P45" s="3">
         <v>14500</v>
       </c>
-      <c r="G45" s="3">
-        <v>12900</v>
-      </c>
-      <c r="H45" s="3">
-        <v>17400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>17500</v>
-      </c>
-      <c r="J45" s="3">
-        <v>17500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>26200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>27300</v>
-      </c>
-      <c r="M45" s="3">
-        <v>27100</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="Q45" s="3">
+        <v>17100</v>
+      </c>
+      <c r="R45" s="3">
+        <v>16900</v>
+      </c>
+      <c r="S45" s="3">
+        <v>17300</v>
+      </c>
+      <c r="T45" s="3">
         <v>26000</v>
       </c>
-      <c r="O45" s="3">
-        <v>14500</v>
-      </c>
-      <c r="P45" s="3">
-        <v>17100</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>16900</v>
-      </c>
-      <c r="R45" s="3">
-        <v>17300</v>
-      </c>
-      <c r="S45" s="3">
-        <v>26000</v>
-      </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>28100</v>
-      </c>
-      <c r="U45" s="3">
-        <v>27400</v>
       </c>
       <c r="V45" s="3">
         <v>27400</v>
       </c>
       <c r="W45" s="3">
+        <v>27400</v>
+      </c>
+      <c r="X45" s="3">
         <v>26200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>24600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>24900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>27600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>41100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>40800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>42100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>40600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>27800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>51000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>51500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>47800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>120200</v>
+      </c>
+      <c r="E46" s="3">
         <v>114900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>111600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>138100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>127600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>139500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>169700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>234300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>229900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>266600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>288600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>333400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>315300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>312600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>293100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>346200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>322600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>318700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>301000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>321800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>284300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>263500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>271900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>299000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>291900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>278100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>266900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>300900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>265100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>272600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>267700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>279800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>248500</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4321,210 +4425,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E48" s="3">
         <v>5700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>9000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>23400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>30000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>33200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>36500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>39500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>42100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>43600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>46700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>51100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>54600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>58200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>62800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>36000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>31100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>32600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>32500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>66900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>34000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>32800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>31200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>62300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>27600</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>498400</v>
+      </c>
+      <c r="E49" s="3">
         <v>501500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>505000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>508700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>512200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>518100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>524800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>531700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>539100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>547000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>553500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>559700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>566100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>572300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>578500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>583700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>590200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>582400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>589600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>596500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>603600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>609100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>616000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>622900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>629900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>636800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>643700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>650700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>657600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>664500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>671500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>678400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>685300</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4624,8 +4737,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4725,109 +4841,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E52" s="3">
         <v>43400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>44800</v>
       </c>
-      <c r="F52" s="3">
-        <v>70700</v>
-      </c>
       <c r="G52" s="3">
-        <v>72200</v>
+        <v>2400</v>
       </c>
       <c r="H52" s="3">
+        <v>66400</v>
+      </c>
+      <c r="I52" s="3">
         <v>71100</v>
       </c>
-      <c r="I52" s="3">
-        <v>64700</v>
-      </c>
       <c r="J52" s="3">
+        <v>58900</v>
+      </c>
+      <c r="K52" s="3">
         <v>61000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>62100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>65600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>69400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>68300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>79300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>76500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>76700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>76000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>76500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>77000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>76600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>78600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>87500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>90500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>88300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>78200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>79200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>79600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>76000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>72100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>4700</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>6100</v>
       </c>
       <c r="AG52" s="3">
         <v>6100</v>
       </c>
       <c r="AH52" s="3">
+        <v>6100</v>
+      </c>
+      <c r="AI52" s="3">
         <v>5700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>24300</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4927,109 +5049,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>665000</v>
+      </c>
+      <c r="E54" s="3">
         <v>665500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>667900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>724800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>720000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>737700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>772700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>840900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>850900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>900600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>934900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>987300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>990700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>994600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>984800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1045400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1031500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1021700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1013900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1048000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1030000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1021300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1039000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1036200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1032000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1027100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1019200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1057100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>961400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>976000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>976500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>995100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>985800</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5065,8 +5193,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5102,109 +5231,113 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E57" s="3">
         <v>8700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>10900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>19700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>20900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>22900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>15100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>15400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>16800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>20900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>19700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>26600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>18700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>20400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>19200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>25200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>16200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>23400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>21400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>19500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>23300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>23900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>23800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>25600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>19900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>23200</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5215,10 +5348,10 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -5304,233 +5437,242 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>173000</v>
+        <v>125000</v>
       </c>
       <c r="E59" s="3">
-        <v>170400</v>
+        <v>126900</v>
       </c>
       <c r="F59" s="3">
-        <v>193100</v>
+        <v>133300</v>
       </c>
       <c r="G59" s="3">
-        <v>187100</v>
+        <v>153200</v>
       </c>
       <c r="H59" s="3">
-        <v>196800</v>
+        <v>133500</v>
       </c>
       <c r="I59" s="3">
-        <v>193100</v>
+        <v>135600</v>
       </c>
       <c r="J59" s="3">
+        <v>147500</v>
+      </c>
+      <c r="K59" s="3">
         <v>226700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>202200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>215600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>218100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>251400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>249500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>244400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>226400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>277600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>261700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>253900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>240000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>274700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>240700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>227000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>225500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>244400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>220200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>217100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>199800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>219300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>187200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>190100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>173400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>179600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>163700</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>195400</v>
+      </c>
+      <c r="E60" s="3">
         <v>181700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>181300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>202100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>198800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>208000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>207800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>245600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>221900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>236500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>241000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>266500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>262600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>259900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>243900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>294300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>282600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>273600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>266600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>293400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>261100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>246200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>250600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>260500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>243500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>238600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>219300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>242600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>211200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>213900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>198900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>199500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>186900</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>4800</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>5800</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>6800</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5607,109 +5749,115 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>23400</v>
+        <v>9100</v>
       </c>
       <c r="E62" s="3">
-        <v>19300</v>
+        <v>9400</v>
       </c>
       <c r="F62" s="3">
-        <v>21300</v>
+        <v>8000</v>
       </c>
       <c r="G62" s="3">
-        <v>23500</v>
+        <v>7800</v>
       </c>
       <c r="H62" s="3">
-        <v>25200</v>
+        <v>7700</v>
       </c>
       <c r="I62" s="3">
-        <v>35200</v>
+        <v>7500</v>
       </c>
       <c r="J62" s="3">
+        <v>14300</v>
+      </c>
+      <c r="K62" s="3">
         <v>37300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>43100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>56500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>68600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>72800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>75800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>77200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>79900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>83200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>81700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>82600</v>
-      </c>
-      <c r="U62" s="3">
-        <v>87800</v>
       </c>
       <c r="V62" s="3">
         <v>87800</v>
       </c>
       <c r="W62" s="3">
+        <v>87800</v>
+      </c>
+      <c r="X62" s="3">
         <v>101900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>106800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>107600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>82900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>76500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>76300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>81500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>83400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>86700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>89600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>97300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>104100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5809,8 +5957,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5910,8 +6061,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6011,109 +6165,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>220600</v>
+      </c>
+      <c r="E66" s="3">
         <v>205100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>200600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>223500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>222200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>233200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>243000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>282900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>265000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>293000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>309600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>339200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>338400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>337100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>323800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>377600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>364300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>356200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>354400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>381200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>363000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>353000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>358300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>343500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>320100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>314900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>300800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>326000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>297900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>303600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>296200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>303700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>290600</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6149,8 +6309,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6250,8 +6411,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6351,8 +6515,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6452,8 +6619,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6553,109 +6723,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-548500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-521000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-506200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-470200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-461900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-447500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-415100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-384100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-344100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-315900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-291200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-269600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-260800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-248000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-236200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-229800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-220300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-216700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-215500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-207900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-202700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-194800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-184500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-176300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-164500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-160800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-151000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-137200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-198800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-187200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-175100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-160900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-154000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6755,8 +6931,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6856,8 +7035,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6957,109 +7139,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>444400</v>
+      </c>
+      <c r="E76" s="3">
         <v>460400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>467200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>501300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>497700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>504500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>529700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>558000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>585900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>607600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>625300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>648100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>652300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>657500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>661000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>667800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>667100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>665600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>659500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>666900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>667000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>668300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>680700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>692700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>711900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>712300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>718400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>731100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>663500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>672400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>680300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>691400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>695200</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7159,215 +7347,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45597</v>
+      </c>
+      <c r="E80" s="2">
         <v>45506</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45415</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45324</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45233</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45142</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45051</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44960</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44862</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44771</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44680</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44589</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44498</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44407</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44316</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44225</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44134</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44043</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43952</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43861</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43770</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43679</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43588</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43497</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43406</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43315</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43224</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43133</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43042</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42951</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42860</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42769</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42671</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-27500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-14700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-36100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-8300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-14400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-32400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-31000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-40000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-28100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-24700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-21600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-8800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-12900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-10300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-9800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-13800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>22500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-9400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-10300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-13300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-6800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-7700</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7403,109 +7600,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>5500</v>
+        <v>1200</v>
       </c>
       <c r="E83" s="3">
-        <v>5900</v>
+        <v>1600</v>
       </c>
       <c r="F83" s="3">
-        <v>5900</v>
+        <v>1600</v>
       </c>
       <c r="G83" s="3">
-        <v>8100</v>
+        <v>2000</v>
       </c>
       <c r="H83" s="3">
-        <v>9000</v>
+        <v>2200</v>
       </c>
       <c r="I83" s="3">
-        <v>9000</v>
+        <v>2500</v>
       </c>
       <c r="J83" s="3">
+        <v>2500</v>
+      </c>
+      <c r="K83" s="3">
         <v>8900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>10600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10100</v>
-      </c>
-      <c r="P83" s="3">
-        <v>9900</v>
       </c>
       <c r="Q83" s="3">
         <v>9900</v>
       </c>
       <c r="R83" s="3">
+        <v>9900</v>
+      </c>
+      <c r="S83" s="3">
         <v>10600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>10100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>10400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>10500</v>
-      </c>
-      <c r="V83" s="3">
-        <v>10900</v>
       </c>
       <c r="W83" s="3">
         <v>10900</v>
       </c>
       <c r="X83" s="3">
+        <v>10900</v>
+      </c>
+      <c r="Y83" s="3">
         <v>10800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>10400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>10300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>10400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>10200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>10300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>10900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>10700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>10400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>10300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>10200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7605,8 +7806,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7706,8 +7910,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7807,8 +8014,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7908,8 +8118,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8009,109 +8222,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E89" s="3">
         <v>3800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-12600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4500</v>
       </c>
-      <c r="H89" s="3">
-        <v>-27800</v>
-      </c>
       <c r="I89" s="3">
-        <v>-42200</v>
+        <v>-26800</v>
       </c>
       <c r="J89" s="3">
+        <v>-40600</v>
+      </c>
+      <c r="K89" s="3">
         <v>9400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-26800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-16500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-24900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>18500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>11500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>17300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-30600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>32200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>22400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>26400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-20300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>43000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>22600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>16300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>31200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>15200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>29300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-18400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>4000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>5200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>11200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-19700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>11800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8147,109 +8366,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="N91" s="3">
         <v>-2100</v>
       </c>
-      <c r="E91" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="O91" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="P91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-2000</v>
       </c>
-      <c r="H91" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="L91" s="3">
+      <c r="R91" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="S91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="T91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="U91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="V91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="W91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="AA91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-1600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="AC91" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-2100</v>
       </c>
-      <c r="N91" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-800</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-500</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-700</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-500</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-3600</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-7000</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-2200</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-6700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8349,8 +8572,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8450,109 +8676,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-15600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-6100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-5400</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8588,31 +8820,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8689,8 +8922,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8790,8 +9026,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8891,8 +9130,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8992,92 +9234,95 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6000</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-200</v>
       </c>
       <c r="G100" s="3">
         <v>-200</v>
       </c>
       <c r="H100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I100" s="3">
         <v>-600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-5100</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-400</v>
       </c>
       <c r="K100" s="3">
         <v>-400</v>
       </c>
       <c r="L100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M100" s="3">
         <v>-600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-8400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-14100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
         <v>0</v>
       </c>
@@ -9085,30 +9330,33 @@
         <v>0</v>
       </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-2000</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
       <c r="AI100" s="3">
         <v>0</v>
       </c>
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>-100</v>
+      <c r="D101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="E101" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>24</v>
+        <v>-1000</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-3500</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>24</v>
@@ -9122,8 +9370,8 @@
       <c r="K101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9194,105 +9442,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E102" s="3">
         <v>600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-21600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-29600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-49000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-28500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-18700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-34400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>16400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-39700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>32300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>25500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-25800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>43100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>21100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>6500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-18400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>13800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>12500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>26000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-24200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>6200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-25000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>5800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2400</v>
       </c>
     </row>
